--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512444_1ºCA1ºCBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512444_1ºCA1ºCBFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5224</v>
+        <v>3.4975</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3878</v>
+        <v>2.868</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1346</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3907</v>
+        <v>2.4295</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1563</v>
+        <v>-0.0974</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5471</v>
+        <v>2.5269</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8505</v>
+        <v>3.0714</v>
       </c>
       <c r="K2" t="n">
-        <v>0.887</v>
+        <v>1.0367</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9635</v>
+        <v>2.0347</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4598</v>
+        <v>-0.6419</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5835</v>
+        <v>0.4922</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4517</v>
+        <v>0.3795</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1383</v>
+        <v>0.3018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3134</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2801</v>
+        <v>1.2726</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0326</v>
+        <v>3.456</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3209</v>
+        <v>4.8659</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2883</v>
+        <v>-1.4099</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7408</v>
+        <v>2.6943</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9448</v>
+        <v>0.9195</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7959</v>
+        <v>1.7748</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6992</v>
+        <v>3.7705</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6595</v>
+        <v>1.7037</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0397</v>
+        <v>2.0668</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9585</v>
+        <v>-1.0762</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7147</v>
+        <v>-0.7842</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9683</v>
+        <v>-0.4915</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8379</v>
+        <v>-0.4052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1304</v>
+        <v>-0.0863</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.092</v>
+        <v>2.2066</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0382</v>
+        <v>4.1701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0538</v>
+        <v>-1.9635</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1606</v>
+        <v>0.9175</v>
       </c>
       <c r="H4" t="n">
-        <v>3.904</v>
+        <v>-0.9473</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2566</v>
+        <v>1.8648</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6987</v>
+        <v>1.8489</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4187</v>
+        <v>0.2105</v>
       </c>
       <c r="L4" t="n">
-        <v>0.28</v>
+        <v>1.6384</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4619</v>
+        <v>-0.9314</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5147</v>
+        <v>-1.1578</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9766</v>
+        <v>0.2264</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.6007</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.2012</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2718</v>
+        <v>-0.7109</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8807</v>
+        <v>-0.3682</v>
       </c>
       <c r="U4" t="n">
-        <v>0.391</v>
+        <v>-0.3427</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.7396</v>
+        <v>1.2211</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3401</v>
+        <v>3.6632</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7572</v>
+        <v>1.9571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4466</v>
+        <v>0.5594</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3106</v>
+        <v>1.3977</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1248</v>
+        <v>1.1032</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3668</v>
+        <v>0.3577</v>
       </c>
       <c r="I5" t="n">
-        <v>0.758</v>
+        <v>0.7456</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4399</v>
+        <v>0.4505</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3599</v>
+        <v>0.3695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6849</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0069</v>
+        <v>-0.0118</v>
       </c>
       <c r="O5" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1678</v>
+        <v>0.075</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0067</v>
+        <v>0.1089</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1745</v>
+        <v>-0.0339</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.6853</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8771</v>
+        <v>0.7271</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9572</v>
+        <v>-0.0418</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8434</v>
+        <v>1.1613</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8859</v>
+        <v>-0.2053</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7293</v>
+        <v>1.3666</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5605</v>
+        <v>1.2402</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1436</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4169</v>
+        <v>1.2402</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7171</v>
+        <v>-0.0789</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0295</v>
+        <v>-0.2053</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3123</v>
+        <v>0.1263</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8002</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.3895</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8005</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9235</v>
+        <v>-0.2813</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2824</v>
+        <v>-0.1237</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.641</v>
+        <v>-0.1576</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5993</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6279</v>
+        <v>0.4996</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6727</v>
+        <v>-0.58</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0448</v>
+        <v>1.0796</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1442</v>
+        <v>0.5305</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1999</v>
+        <v>-0.1924</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3442</v>
+        <v>0.7229</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2017</v>
+        <v>0.0291</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.0359</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2017</v>
+        <v>0.065</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0575</v>
+        <v>0.5014</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1999</v>
+        <v>-0.1565</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1425</v>
+        <v>0.6579</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3163</v>
+        <v>-0.2257</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1289</v>
+        <v>-0.2196</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1874</v>
+        <v>-0.006</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1499</v>
+        <v>0.3799</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2389</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.089</v>
+        <v>-0.4875</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3757</v>
+        <v>5.1452</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0797</v>
+        <v>3.9574</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4554</v>
+        <v>1.1878</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6056</v>
+        <v>4.82</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5580000000000001</v>
+        <v>4.5363</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1636</v>
+        <v>0.2837</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2299</v>
+        <v>0.3252</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5789</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2918</v>
+        <v>0.9041</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4001</v>
+        <v>-4.0895</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2258</v>
+        <v>0.5394</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0334</v>
+        <v>0.4679</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2593</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.7732</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0116</v>
+        <v>0.1602</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0991</v>
+        <v>0.3016</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1107</v>
+        <v>-0.1415</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.3618</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2181</v>
+        <v>-1.1084</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7268</v>
+        <v>1.4703</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0545</v>
+        <v>0.6828</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0964</v>
+        <v>-0.5413</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0419</v>
+        <v>1.2241</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5631</v>
+        <v>-0.321</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1218</v>
+        <v>-0.5671</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6849</v>
+        <v>0.2461</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.2017</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6446</v>
+        <v>0.0083</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0525</v>
+        <v>-0.21</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1574</v>
+        <v>-0.645</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4428</v>
+        <v>-0.0209</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7146</v>
+        <v>-0.624</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6348</v>
+        <v>-0.6936</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0797</v>
+        <v>-1.1084</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4449</v>
+        <v>0.4148</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2018</v>
+        <v>0.2365</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0418</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8366</v>
+        <v>-0.9302</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2849</v>
+        <v>0.2527</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1228</v>
+        <v>-0.5355</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6446</v>
+        <v>-0.2575</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4782</v>
+        <v>-0.278</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1401</v>
+        <v>-1.4993</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5686</v>
+        <v>-1.621</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4285</v>
+        <v>0.1217</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.6756</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2009</v>
+        <v>-2.1459</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4554</v>
+        <v>1.4703</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4566</v>
+        <v>0.7084</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8289</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2855</v>
+        <v>1.3702</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2021</v>
+        <v>-1.384</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3719</v>
+        <v>-1.4841</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1699</v>
+        <v>0.1001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9946</v>
+        <v>-0.4342</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0246</v>
+        <v>-0.3821</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0301</v>
+        <v>-0.0522</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2936</v>
+        <v>-2.478</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1006</v>
+        <v>-2.0405</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.193</v>
+        <v>-0.4375</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2284</v>
+        <v>-1.2695</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3153</v>
+        <v>-1.344</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0868</v>
+        <v>0.0745</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.578</v>
+        <v>-0.5629</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6504</v>
+        <v>-0.7065</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6573</v>
+        <v>-0.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0069</v>
+        <v>-0.0066</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0649</v>
+        <v>-0.2349</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3223</v>
+        <v>-0.3092</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2573</v>
+        <v>0.0743</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7225</v>
+        <v>-3.0792</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9492</v>
+        <v>-1.0512</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7733</v>
+        <v>-2.028</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2907</v>
+        <v>-2.3295</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1132</v>
+        <v>-2.1316</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1775</v>
+        <v>-0.1979</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.176</v>
+        <v>-1.1453</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.256</v>
+        <v>-1.2264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1147</v>
+        <v>-1.1842</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8572</v>
+        <v>-0.9052</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2575</v>
+        <v>-0.2789</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3679</v>
+        <v>0.0819</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2268</v>
+        <v>0.0941</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1411</v>
+        <v>-0.0122</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.799899999999999</v>
+        <v>5.140700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8219</v>
+        <v>9.045900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.022</v>
+        <v>-3.905200000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>9.389399999999998</v>
+        <v>9.3751</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.0334</v>
+        <v>-4.046100000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>13.4229</v>
+        <v>13.4214</v>
       </c>
       <c r="J14" t="n">
-        <v>13.906</v>
+        <v>15.1501</v>
       </c>
       <c r="K14" t="n">
-        <v>4.113199999999999</v>
+        <v>4.8217</v>
       </c>
       <c r="L14" t="n">
-        <v>9.792800000000002</v>
+        <v>10.3285</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.5167</v>
+        <v>-5.775</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.146600000000001</v>
+        <v>-8.868</v>
       </c>
       <c r="O14" t="n">
-        <v>3.63</v>
+        <v>3.0928</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9738</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.0034</v>
+        <v>-11.6843</v>
       </c>
       <c r="R14" t="n">
-        <v>11.0033</v>
+        <v>10.7104</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3897</v>
+        <v>-2.0399</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5994</v>
+        <v>-1.0845</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7904000000000001</v>
+        <v>-0.9554</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1997</v>
+        <v>-1.2211</v>
       </c>
       <c r="W14" t="n">
-        <v>6.5185</v>
+        <v>6.664199999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.7182</v>
+        <v>-7.8854</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8584</v>
+        <v>3.8567</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3863</v>
+        <v>6.3382</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5279</v>
+        <v>-2.4815</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3108</v>
+        <v>1.3411</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7751</v>
+        <v>1.8161</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4643</v>
+        <v>-0.475</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7265</v>
+        <v>3.9173</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4829</v>
+        <v>2.6121</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2436</v>
+        <v>1.3052</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4157</v>
+        <v>-2.5762</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7078</v>
+        <v>-0.796</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7079</v>
+        <v>-1.7802</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4073</v>
+        <v>0.4056</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4603</v>
+        <v>0.1735</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.053</v>
+        <v>0.2321</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2666</v>
+        <v>3.4687</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7877</v>
+        <v>2.524</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4789</v>
+        <v>0.9447</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9319</v>
+        <v>2.8891</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9758</v>
+        <v>1.9653</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9237</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4191</v>
+        <v>3.4995</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6193</v>
+        <v>2.689</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4873</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6434</v>
+        <v>-0.7236</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1562</v>
+        <v>0.1132</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1346</v>
+        <v>0.3849</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6312</v>
+        <v>-0.0018</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7658</v>
+        <v>0.3867</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7281</v>
+        <v>1.8932</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9209</v>
+        <v>1.357</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8073</v>
+        <v>0.5362</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6441</v>
+        <v>0.6745</v>
       </c>
       <c r="H17" t="n">
-        <v>1.842</v>
+        <v>1.8658</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1979</v>
+        <v>-1.1913</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5454</v>
+        <v>0.6454</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2215</v>
+        <v>1.2855</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6761</v>
+        <v>-0.6401</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0987</v>
+        <v>0.029</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6206</v>
+        <v>0.5803</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4844</v>
+        <v>0.5819</v>
       </c>
       <c r="T17" t="n">
-        <v>1.176</v>
+        <v>0.4642</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3084</v>
+        <v>0.1177</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1819</v>
+        <v>0.1506</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3638</v>
+        <v>-0.0201</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1819</v>
+        <v>0.1707</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7199</v>
+        <v>0.7274</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2468</v>
+        <v>0.2345</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4731</v>
+        <v>0.4929</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8854</v>
+        <v>0.9865</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9615</v>
+        <v>1.0187</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0762</v>
+        <v>-0.0322</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1654</v>
+        <v>-0.2591</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7147</v>
+        <v>-0.7842</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7618</v>
+        <v>-0.4405</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.709</v>
+        <v>-0.4808</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0528</v>
+        <v>0.0404</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.6389</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5203</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0558</v>
+        <v>0.0441</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3109</v>
+        <v>-0.6126</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7823</v>
+        <v>0.0585</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5285</v>
+        <v>-0.6711</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8305</v>
+        <v>-0.5824</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8743</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0438</v>
+        <v>-0.6645</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4803</v>
+        <v>-0.0302</v>
       </c>
       <c r="N19" t="n">
-        <v>0.092</v>
+        <v>-0.0236</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5723</v>
+        <v>-0.0066</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8005</v>
+        <v>0.1947</v>
       </c>
       <c r="S19" t="n">
-        <v>0.735</v>
+        <v>-0.221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0888</v>
+        <v>-0.1006</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8238</v>
+        <v>-0.1204</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3995</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9221</v>
+        <v>-0.7523</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2597</v>
+        <v>-0.1874</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6624</v>
+        <v>-0.5648</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0908</v>
+        <v>-2.3358</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6493</v>
+        <v>-0.7779</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4416</v>
+        <v>-1.5579</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3327</v>
+        <v>-0.7136</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2653</v>
+        <v>-0.803</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.598</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7582</v>
+        <v>-1.6222</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9146</v>
+        <v>0.0251</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8435</v>
+        <v>-1.6473</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3691</v>
+        <v>0.5572</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0738</v>
+        <v>0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2953</v>
+        <v>0.5258</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1998</v>
+        <v>2.4421</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9837</v>
+        <v>-0.9303</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9136</v>
+        <v>-0.4938</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4365</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5773</v>
+        <v>-1.3421</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09379999999999999</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6711</v>
+        <v>-1.3421</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.598</v>
+        <v>-0.6645</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0207</v>
+        <v>-0.6776</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0138</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0069</v>
+        <v>-0.6776</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.2171</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3156</v>
+        <v>0.1707</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2908</v>
+        <v>0.0464</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0517</v>
+        <v>-1.4256</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6069</v>
+        <v>2.455</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4449</v>
+        <v>-3.8806</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3423</v>
+        <v>-0.7345</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.7924</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3423</v>
+        <v>-2.5269</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.678</v>
+        <v>2.0535</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2.6608</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.678</v>
+        <v>-0.6073</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6643</v>
+        <v>-2.788</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6643</v>
+        <v>-1.9197</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2001</v>
+        <v>1.7526</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0905</v>
+        <v>0.5563</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0711</v>
+        <v>0.3489</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0193</v>
+        <v>0.2074</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.8316</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1378</v>
+        <v>-1.7906</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7747</v>
+        <v>-0.9593</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9125</v>
+        <v>-0.8313</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7581</v>
+        <v>-3.119</v>
       </c>
       <c r="H23" t="n">
-        <v>1.789</v>
+        <v>-0.6224</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5471</v>
+        <v>-2.4966</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8507</v>
+        <v>-0.2164</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5611</v>
+        <v>0.367</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7104</v>
+        <v>-0.5835</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6088</v>
+        <v>-2.9025</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7721</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8367</v>
+        <v>-1.9131</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2003</v>
+        <v>-2.1421</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1802</v>
+        <v>0.4968</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.1781</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1048</v>
+        <v>0.3186</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>1.2211</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.9994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4261</v>
+        <v>-3.4703</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3568</v>
+        <v>-2.3384</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0693</v>
+        <v>-1.1319</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.7754</v>
+        <v>-3.8032</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6995</v>
+        <v>-1.7447</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0759</v>
+        <v>-2.0585</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3322</v>
+        <v>-1.2585</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.578</v>
+        <v>-0.5619</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7542</v>
+        <v>-0.6967</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4432</v>
+        <v>-2.5447</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3217</v>
+        <v>-1.3618</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0508</v>
+        <v>-0.0565</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0243</v>
+        <v>-0.1061</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0265</v>
+        <v>0.0496</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3733</v>
+        <v>-4.5283</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8263</v>
+        <v>-4.087</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.547</v>
+        <v>-0.4413</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.1413</v>
+        <v>-3.0599</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5413</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5833</v>
+        <v>-2.5186</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1391</v>
+        <v>-1.8917</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5926</v>
+        <v>-0.4822</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5465</v>
+        <v>-1.4094</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0022</v>
+        <v>-1.1682</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0346</v>
+        <v>-0.0591</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0368</v>
+        <v>-1.1091</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.232</v>
+        <v>0.5316</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1466</v>
+        <v>0.2778</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.2538</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.799600000000002</v>
+        <v>-4.1671</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0222</v>
+        <v>3.905199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.821699999999999</v>
+        <v>-8.072199999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.389399999999998</v>
+        <v>-9.375</v>
       </c>
       <c r="H26" t="n">
-        <v>4.033399999999999</v>
+        <v>4.046300000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-13.4228</v>
+        <v>-13.4214</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5166</v>
+        <v>5.7751</v>
       </c>
       <c r="K26" t="n">
-        <v>8.146699999999999</v>
+        <v>8.868099999999998</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.6301</v>
+        <v>-3.0931</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.906</v>
+        <v>-15.1501</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.1131</v>
+        <v>-4.8218</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.7926</v>
+        <v>-10.3285</v>
       </c>
       <c r="P26" t="n">
-        <v>1.0004</v>
+        <v>0.9736000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.0032</v>
+        <v>-10.7105</v>
       </c>
       <c r="R26" t="n">
-        <v>12.0034</v>
+        <v>11.6842</v>
       </c>
       <c r="S26" t="n">
-        <v>2.389699999999999</v>
+        <v>3.0134</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7903000000000002</v>
+        <v>0.9553</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5992</v>
+        <v>2.0581</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1998</v>
+        <v>1.221100000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>7.718200000000001</v>
+        <v>7.8853</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.5185</v>
+        <v>-6.664199999999999</v>
       </c>
     </row>
   </sheetData>
